--- a/TestCases.xlsx
+++ b/TestCases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80B1E047-68AB-4115-9C3C-E1D56443757A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03E96429-F0EB-45BE-9B92-8739171AFF67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -325,9 +325,6 @@
     <t>The search results related to "Interstellar" are displayed</t>
   </si>
   <si>
-    <t>John</t>
-  </si>
-  <si>
     <t>TC-Functional-02</t>
   </si>
   <si>
@@ -548,6 +545,9 @@
   </si>
   <si>
     <t>The Manage Movies and Add New Movie options are available. The movie information is accepted, and the new movie is published successfully. A confirmation message is displayed in the top-right corner of the page. The newly added movie information is matches the information entered by the administrator and is displayed correctly.</t>
+  </si>
+  <si>
+    <t>William</t>
   </si>
 </sst>
 </file>
@@ -1328,252 +1328,252 @@
         <v>20</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="203.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="160.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="183" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="162.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>128</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>20</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1584,6 +1584,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="b0a8175e-3648-4aae-9c99-37c63d4dc7cd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F5C6D90DF4CC87499920A83C31039441" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d32b801572f3d6df791578ebb81ec19">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="b0a8175e-3648-4aae-9c99-37c63d4dc7cd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a5ead7bcc508272ec5be004b8d24044c" ns3:_="">
     <xsd:import namespace="b0a8175e-3648-4aae-9c99-37c63d4dc7cd"/>
@@ -1733,24 +1750,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="b0a8175e-3648-4aae-9c99-37c63d4dc7cd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A040B21F-45AD-4329-8FE2-181D62A0D400}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171441CA-C744-4496-8AD4-091A8AA28544}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b0a8175e-3648-4aae-9c99-37c63d4dc7cd"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BF0DAE0-EED5-453C-B978-206C21D2B75F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1766,28 +1790,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{171441CA-C744-4496-8AD4-091A8AA28544}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b0a8175e-3648-4aae-9c99-37c63d4dc7cd"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A040B21F-45AD-4329-8FE2-181D62A0D400}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>